--- a/results/phi4_14b/comparison_GoTPlainLLM/GoTPlainLLM_evaluated.xlsx
+++ b/results/phi4_14b/comparison_GoTPlainLLM/GoTPlainLLM_evaluated.xlsx
@@ -505,35 +505,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.01010100960871342</v>
+        <v>0.2201257813921523</v>
       </c>
       <c r="D2" t="n">
-        <v>7.188271943170174e-260</v>
+        <v>2.027317064172704e-155</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3382570147514343</v>
+        <v>0.6062899231910706</v>
       </c>
       <c r="F2" t="n">
-        <v>12.42500000000001</v>
+        <v>16.45019067796611</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06717123935666983</v>
+        <v>0.6877956480605487</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3069306930693069</v>
       </c>
     </row>
     <row r="3">
@@ -546,35 +548,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.08333333146701394</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>8.087494814426946e-232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3607856035232544</v>
+        <v>0.4632394313812256</v>
       </c>
       <c r="F3" t="n">
-        <v>12.42500000000001</v>
+        <v>39.02767581475129</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6513761467889908</v>
+        <v>4.275229357798165</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2307692307692308</v>
       </c>
     </row>
     <row r="4">
@@ -587,35 +591,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.2194092782011431</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2.853552648457251e-156</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2861286401748657</v>
+        <v>0.5087727904319763</v>
       </c>
       <c r="F4" t="n">
-        <v>12.42500000000001</v>
+        <v>27.79104591836736</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07585470085470085</v>
+        <v>0.4636752136752137</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -628,35 +634,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.2471264320869666</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.01747257096087728</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2819922566413879</v>
+        <v>0.5634866952896118</v>
       </c>
       <c r="F5" t="n">
-        <v>12.42500000000001</v>
+        <v>39.7559782608696</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05810147299509002</v>
+        <v>0.5973813420621932</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
@@ -669,35 +677,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01273885288652687</v>
+        <v>0.2330827018689582</v>
       </c>
       <c r="D6" t="n">
-        <v>7.842246496009318e-255</v>
+        <v>1.874738583366479e-155</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3198220431804657</v>
+        <v>0.559995710849762</v>
       </c>
       <c r="F6" t="n">
-        <v>12.42500000000001</v>
+        <v>23.97508960573478</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08160919540229886</v>
+        <v>0.7091954022988506</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2045454545454545</v>
       </c>
     </row>
     <row r="7">
@@ -710,35 +720,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.004032257864935623</v>
+        <v>0.1618886986692981</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3.528448916709317e-82</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3422526717185974</v>
+        <v>0.5546762943267822</v>
       </c>
       <c r="F7" t="n">
-        <v>12.42500000000001</v>
+        <v>16.54755528255532</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02065755018911842</v>
+        <v>0.1786441664242072</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2682926829268293</v>
       </c>
     </row>
     <row r="8">
@@ -751,35 +763,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.205714281172898</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>8.952333798159982e-156</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3306046426296234</v>
+        <v>0.6030941605567932</v>
       </c>
       <c r="F8" t="n">
-        <v>12.42500000000001</v>
+        <v>23.47012983425415</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04930555555555555</v>
+        <v>0.48125</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.1525423728813559</v>
       </c>
     </row>
     <row r="9">
@@ -792,27 +806,29 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.006993006649469429</v>
+        <v>0.1719901677153501</v>
       </c>
       <c r="D9" t="n">
-        <v>4.626996437597695e-283</v>
+        <v>3.879804140492458e-156</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3232488930225372</v>
+        <v>0.5681236386299133</v>
       </c>
       <c r="F9" t="n">
-        <v>12.42500000000001</v>
+        <v>35.69700980392159</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04113557358053303</v>
+        <v>0.3951332560834299</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
@@ -820,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1780821917808219</v>
       </c>
     </row>
     <row r="10">
@@ -833,35 +849,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.1041666638428338</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1.396161808312207e-235</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3218375742435455</v>
+        <v>0.5290889739990234</v>
       </c>
       <c r="F10" t="n">
-        <v>12.42500000000001</v>
+        <v>13.94900000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04695767195767196</v>
+        <v>0.1858465608465608</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.07216494845360824</v>
       </c>
     </row>
     <row r="11">
@@ -874,35 +892,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.006756756424625656</v>
+        <v>0.1557177574227007</v>
       </c>
       <c r="D11" t="n">
-        <v>3.199290466293744e-295</v>
+        <v>2.666523432317515e-80</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3080631196498871</v>
+        <v>0.5482152104377747</v>
       </c>
       <c r="F11" t="n">
-        <v>12.42500000000001</v>
+        <v>29.03810071574645</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03881902679059596</v>
+        <v>0.3603061782394751</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -915,35 +935,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.1975308599489103</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.003872628873636948</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3184725940227509</v>
+        <v>0.6138515472412109</v>
       </c>
       <c r="F12" t="n">
-        <v>12.42500000000001</v>
+        <v>38.22492549335482</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04043280182232346</v>
+        <v>0.3997722095671982</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.1379310344827586</v>
       </c>
     </row>
     <row r="13">
@@ -956,35 +978,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.006644517945718055</v>
+        <v>0.3239436577310499</v>
       </c>
       <c r="D13" t="n">
-        <v>1.737745674680046e-291</v>
+        <v>0.03848960639779165</v>
       </c>
       <c r="E13" t="n">
-        <v>0.326636791229248</v>
+        <v>0.5766304731369019</v>
       </c>
       <c r="F13" t="n">
-        <v>12.42500000000001</v>
+        <v>53.01235172413797</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0393569844789357</v>
+        <v>0.4235033259423504</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4214876033057851</v>
       </c>
     </row>
     <row r="14">
@@ -997,35 +1021,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.1940298467265662</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2.899386359683304e-80</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3217796385288239</v>
+        <v>0.6058722138404846</v>
       </c>
       <c r="F14" t="n">
-        <v>12.42500000000001</v>
+        <v>23.83684272300471</v>
       </c>
       <c r="G14" t="n">
-        <v>0.03944444444444444</v>
+        <v>0.3355555555555556</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.1549295774647887</v>
       </c>
     </row>
     <row r="15">
@@ -1038,35 +1064,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.2169811270914917</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.03535154882114189</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3361954092979431</v>
+        <v>0.5649368762969971</v>
       </c>
       <c r="F15" t="n">
-        <v>12.42500000000001</v>
+        <v>43.6460872528971</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1428571428571428</v>
+        <v>1.223340040241449</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1509433962264151</v>
       </c>
     </row>
     <row r="16">
@@ -1079,27 +1107,29 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.2891566215125563</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>4.667647058635137e-155</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3227388560771942</v>
+        <v>0.6510640382766724</v>
       </c>
       <c r="F16" t="n">
-        <v>12.42500000000001</v>
+        <v>47.20727272727277</v>
       </c>
       <c r="G16" t="n">
-        <v>0.101283880171184</v>
+        <v>1.002853067047076</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
@@ -1107,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="17">
@@ -1120,35 +1150,37 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.158139530210925</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3.534928643185659e-232</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3224216401576996</v>
+        <v>0.5533502697944641</v>
       </c>
       <c r="F17" t="n">
-        <v>12.42500000000001</v>
+        <v>26.35875000000004</v>
       </c>
       <c r="G17" t="n">
-        <v>0.09543010752688172</v>
+        <v>0.6182795698924731</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="18">
@@ -1161,35 +1193,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.2281368784272579</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>7.767617537256228e-80</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3511787950992584</v>
+        <v>0.5974078774452209</v>
       </c>
       <c r="F18" t="n">
-        <v>12.42500000000001</v>
+        <v>37.71025412087914</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02764797507788162</v>
+        <v>0.2858255451713396</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="19">
@@ -1202,35 +1236,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.1976047865099143</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2.887729973462374e-80</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3164240121841431</v>
+        <v>0.601162850856781</v>
       </c>
       <c r="F19" t="n">
-        <v>12.42500000000001</v>
+        <v>27.60816425120777</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04680290046143705</v>
+        <v>0.3328938694792353</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.2125984251968504</v>
       </c>
     </row>
     <row r="20">
@@ -1243,35 +1279,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.008032128120514206</v>
+        <v>0.2125340554890155</v>
       </c>
       <c r="D20" t="n">
-        <v>1.21304235279905e-268</v>
+        <v>0.01244871695417394</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3357276916503906</v>
+        <v>0.5857091546058655</v>
       </c>
       <c r="F20" t="n">
-        <v>12.42500000000001</v>
+        <v>28.75781835205996</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05039034776437189</v>
+        <v>0.4996451383960255</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.1603053435114504</v>
       </c>
     </row>
     <row r="21">
@@ -1284,35 +1322,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.1588235257515572</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4.668372612564776e-157</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3344107270240784</v>
+        <v>0.5306360721588135</v>
       </c>
       <c r="F21" t="n">
-        <v>12.42500000000001</v>
+        <v>22.23763506625895</v>
       </c>
       <c r="G21" t="n">
-        <v>0.04022662889518414</v>
+        <v>0.2770538243626062</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.125</v>
+      </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0136986301369863</v>
+        <v>0.03940886699507389</v>
       </c>
     </row>
     <row r="22">
@@ -1325,35 +1365,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.3294663524765694</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>7.278906466481833e-79</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3496818244457245</v>
+        <v>0.6370041370391846</v>
       </c>
       <c r="F22" t="n">
-        <v>12.42500000000001</v>
+        <v>34.80610502418324</v>
       </c>
       <c r="G22" t="n">
-        <v>0.04303030303030303</v>
+        <v>0.6387878787878788</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.2647058823529412</v>
       </c>
     </row>
     <row r="23">
@@ -1366,35 +1408,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.005847952928251443</v>
+        <v>0.1716937320882209</v>
       </c>
       <c r="D23" t="n">
-        <v>1.811128572821972e-307</v>
+        <v>0.0002153634457716161</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3417599201202393</v>
+        <v>0.5935307741165161</v>
       </c>
       <c r="F23" t="n">
-        <v>12.42500000000001</v>
+        <v>34.42153434800497</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03261368856224162</v>
+        <v>0.2668810289389068</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2708333333333334</v>
       </c>
     </row>
     <row r="24">
@@ -1407,35 +1451,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.2333333284222223</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.02289964820840968</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3145212233066559</v>
+        <v>0.6228812336921692</v>
       </c>
       <c r="F24" t="n">
-        <v>12.42500000000001</v>
+        <v>40.53012682137077</v>
       </c>
       <c r="G24" t="n">
-        <v>0.109062980030722</v>
+        <v>1.288786482334869</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3388429752066116</v>
       </c>
     </row>
     <row r="25">
@@ -1448,35 +1494,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.2977099187585223</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1.030439770766457e-78</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3218568563461304</v>
+        <v>0.6429927349090576</v>
       </c>
       <c r="F25" t="n">
-        <v>12.42500000000001</v>
+        <v>47.54985829959514</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1070889894419306</v>
+        <v>1.253393665158371</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3670886075949367</v>
       </c>
     </row>
     <row r="26">
@@ -1489,35 +1537,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.2660550409540444</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1.178485891180151e-78</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3182421326637268</v>
+        <v>0.6297150850296021</v>
       </c>
       <c r="F26" t="n">
-        <v>12.42500000000001</v>
+        <v>40.08553278688524</v>
       </c>
       <c r="G26" t="n">
-        <v>0.123050259965338</v>
+        <v>1.162911611785095</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -1530,35 +1580,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.3605150164998436</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.1186020801410399</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3122285008430481</v>
+        <v>0.6553923487663269</v>
       </c>
       <c r="F27" t="n">
-        <v>12.42500000000001</v>
+        <v>35.95960304054054</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09712722298221614</v>
+        <v>0.905608755129959</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4252873563218391</v>
       </c>
     </row>
     <row r="28">
@@ -1571,35 +1623,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.2361623567614821</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>4.645779704255236e-155</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3209810554981232</v>
+        <v>0.6078421473503113</v>
       </c>
       <c r="F28" t="n">
-        <v>12.42500000000001</v>
+        <v>27.47001287415517</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1075757575757576</v>
+        <v>1.31969696969697</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3749999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1612,35 +1666,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.265402838651423</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>3.729438571895397e-155</v>
       </c>
       <c r="E29" t="n">
-        <v>0.317456990480423</v>
+        <v>0.6346973776817322</v>
       </c>
       <c r="F29" t="n">
-        <v>12.42500000000001</v>
+        <v>38.85805031446543</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1232638888888889</v>
+        <v>1.071180555555556</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="30">
@@ -1653,35 +1709,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.04733727709814085</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1.349112716410584e-155</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4068427383899689</v>
+        <v>0.416518896818161</v>
       </c>
       <c r="F30" t="n">
-        <v>12.42500000000001</v>
+        <v>36.02919354838713</v>
       </c>
       <c r="G30" t="n">
-        <v>0.71</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31">
@@ -1694,35 +1752,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.06289308069301057</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1.482112406539712e-155</v>
       </c>
       <c r="E31" t="n">
-        <v>0.405496746301651</v>
+        <v>0.4403652250766754</v>
       </c>
       <c r="F31" t="n">
-        <v>12.42500000000001</v>
+        <v>34.22715789473688</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6893203883495146</v>
+        <v>8.25242718446602</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2436974789915966</v>
       </c>
     </row>
     <row r="32">
@@ -1735,35 +1795,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.098039214077278</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1.960114543996295e-155</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4001372754573822</v>
+        <v>0.4697017669677734</v>
       </c>
       <c r="F32" t="n">
-        <v>12.42500000000001</v>
+        <v>38.82620155038765</v>
       </c>
       <c r="G32" t="n">
-        <v>0.71</v>
+        <v>5.5</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="33">
@@ -1776,19 +1838,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.1626016211117723</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>2.643833696368049e-155</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3932636678218842</v>
+        <v>0.5117695927619934</v>
       </c>
       <c r="F33" t="n">
-        <v>12.42500000000001</v>
+        <v>35.00630612244899</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1966759002770083</v>
+        <v>1.157894736842105</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1796,15 +1858,17 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1578947368421053</v>
       </c>
     </row>
     <row r="34">
@@ -1817,35 +1881,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.2285714236480727</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>2.005256986190514e-155</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3809874057769775</v>
+        <v>0.5366058349609375</v>
       </c>
       <c r="F34" t="n">
-        <v>12.42500000000001</v>
+        <v>30.21060344827589</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1031976744186047</v>
+        <v>0.7252906976744186</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1549295774647887</v>
       </c>
     </row>
     <row r="35">
@@ -1858,35 +1924,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.2307692261491207</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1.456281036629997e-155</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3331394195556641</v>
+        <v>0.5998542308807373</v>
       </c>
       <c r="F35" t="n">
-        <v>12.42500000000001</v>
+        <v>23.42578859060401</v>
       </c>
       <c r="G35" t="n">
-        <v>0.06217162872154115</v>
+        <v>0.5621716287215411</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1891891891891892</v>
       </c>
     </row>
     <row r="36">
@@ -1899,35 +1967,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.2153846104204143</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2.459398402756693e-155</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3015691339969635</v>
+        <v>0.5755105018615723</v>
       </c>
       <c r="F36" t="n">
-        <v>12.42500000000001</v>
+        <v>17.82568102073367</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1125198098256735</v>
+        <v>1.245641838351822</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1891891891891892</v>
       </c>
     </row>
     <row r="37">
@@ -1940,35 +2010,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.2452830138697046</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1.359833238477108e-78</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3549112677574158</v>
+        <v>0.6297886371612549</v>
       </c>
       <c r="F37" t="n">
-        <v>12.42500000000001</v>
+        <v>37.90426900584799</v>
       </c>
       <c r="G37" t="n">
-        <v>0.07529162248144221</v>
+        <v>1.091198303287381</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4845360824742268</v>
       </c>
     </row>
     <row r="38">
@@ -1981,35 +2053,37 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.2159999950028801</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>4.177942492722784e-155</v>
       </c>
       <c r="E38" t="n">
-        <v>0.353282243013382</v>
+        <v>0.5601202249526978</v>
       </c>
       <c r="F38" t="n">
-        <v>12.42500000000001</v>
+        <v>14.27382022471912</v>
       </c>
       <c r="G38" t="n">
-        <v>0.09184993531694696</v>
+        <v>0.944372574385511</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2708333333333334</v>
       </c>
     </row>
     <row r="39">
@@ -2022,35 +2096,37 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.1729729681519359</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>2.690253750949746e-155</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3316194117069244</v>
+        <v>0.5925518274307251</v>
       </c>
       <c r="F39" t="n">
-        <v>12.42500000000001</v>
+        <v>41.14184210526318</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1047197640117994</v>
+        <v>0.6887905604719764</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.1452991452991453</v>
       </c>
     </row>
     <row r="40">
@@ -2063,35 +2139,37 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.2262773673397625</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>3.711174997260935e-79</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2845998406410217</v>
+        <v>0.523645281791687</v>
       </c>
       <c r="F40" t="n">
-        <v>12.42500000000001</v>
+        <v>25.17939393939398</v>
       </c>
       <c r="G40" t="n">
-        <v>0.07819383259911894</v>
+        <v>0.7026431718061674</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2307692307692308</v>
       </c>
     </row>
     <row r="41">
@@ -2104,35 +2182,37 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.1989528751251337</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1.511314035121895e-79</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2805698215961456</v>
+        <v>0.5371474027633667</v>
       </c>
       <c r="F41" t="n">
-        <v>12.42500000000001</v>
+        <v>31.28214245810057</v>
       </c>
       <c r="G41" t="n">
-        <v>0.04869684499314129</v>
+        <v>0.4917695473251029</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2405063291139241</v>
       </c>
     </row>
     <row r="42">
@@ -2145,35 +2225,37 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01273885288652687</v>
+        <v>0.2847457577165183</v>
       </c>
       <c r="D42" t="n">
-        <v>7.842246496009318e-255</v>
+        <v>8.80739104117219e-79</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3200334906578064</v>
+        <v>0.5993292331695557</v>
       </c>
       <c r="F42" t="n">
-        <v>12.42500000000001</v>
+        <v>47.20628289473686</v>
       </c>
       <c r="G42" t="n">
-        <v>0.08114285714285714</v>
+        <v>0.8594285714285714</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="43">
@@ -2186,35 +2268,37 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.2078651635494257</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>7.851922773836407e-79</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3462300896644592</v>
+        <v>0.6243407726287842</v>
       </c>
       <c r="F43" t="n">
-        <v>12.42500000000001</v>
+        <v>24.61820635136979</v>
       </c>
       <c r="G43" t="n">
-        <v>0.06580166821130677</v>
+        <v>1.034291010194625</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.1891891891891892</v>
       </c>
     </row>
     <row r="44">
@@ -2227,35 +2311,37 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.1831501783681521</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>5.32410154959273e-79</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3189048171043396</v>
+        <v>0.6311661005020142</v>
       </c>
       <c r="F44" t="n">
-        <v>12.42500000000001</v>
+        <v>14.84206632653061</v>
       </c>
       <c r="G44" t="n">
-        <v>0.08151549942594719</v>
+        <v>0.7841561423650976</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2105263157894737</v>
       </c>
     </row>
     <row r="45">
@@ -2268,35 +2354,37 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.1313131289823034</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>2.328008250173485e-160</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3425029814243317</v>
+        <v>0.5515757203102112</v>
       </c>
       <c r="F45" t="n">
-        <v>12.42500000000001</v>
+        <v>14.61376237623762</v>
       </c>
       <c r="G45" t="n">
-        <v>0.01946805593638607</v>
+        <v>0.1258568686591719</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1935483870967742</v>
       </c>
     </row>
     <row r="46">
@@ -2309,35 +2397,37 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.3433813851825844</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>0.04451783982059418</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3373959362506866</v>
+        <v>0.6453493237495422</v>
       </c>
       <c r="F46" t="n">
-        <v>12.42500000000001</v>
+        <v>56.65225684931511</v>
       </c>
       <c r="G46" t="n">
-        <v>0.01966214345056771</v>
+        <v>0.3793962891165882</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="47">
@@ -2350,27 +2440,29 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.2185566976151345</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.0001941507012433737</v>
       </c>
       <c r="E47" t="n">
-        <v>0.358601450920105</v>
+        <v>0.610046923160553</v>
       </c>
       <c r="F47" t="n">
-        <v>12.42500000000001</v>
+        <v>22.5976737967915</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0282981267437226</v>
+        <v>0.2287764049422081</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
@@ -2378,7 +2470,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2156862745098039</v>
       </c>
     </row>
     <row r="48">
@@ -2391,35 +2483,37 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2307692261316569</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>4.204956870067577e-155</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3561545312404633</v>
+        <v>0.624326765537262</v>
       </c>
       <c r="F48" t="n">
-        <v>12.42500000000001</v>
+        <v>34.48713815789478</v>
       </c>
       <c r="G48" t="n">
-        <v>0.15203426124197</v>
+        <v>1.644539614561028</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2660550458715596</v>
       </c>
     </row>
     <row r="49">
@@ -2432,35 +2526,37 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.2713567789863893</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1.035880491824639e-78</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3449079990386963</v>
+        <v>0.6271861791610718</v>
       </c>
       <c r="F49" t="n">
-        <v>12.42500000000001</v>
+        <v>44.44180555555556</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1368015414258189</v>
+        <v>1.18111753371869</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2241379310344828</v>
       </c>
     </row>
     <row r="50">
@@ -2473,35 +2569,37 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.1991701198450441</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>7.642947701111475e-79</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3456511199474335</v>
+        <v>0.5884968638420105</v>
       </c>
       <c r="F50" t="n">
-        <v>12.42500000000001</v>
+        <v>34.50517605633806</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1360153256704981</v>
+        <v>1.580459770114943</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2105263157894737</v>
       </c>
     </row>
     <row r="51">
@@ -2514,35 +2612,37 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.2687746985611399</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>0.02181214498771713</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3437384366989136</v>
+        <v>0.6134772896766663</v>
       </c>
       <c r="F51" t="n">
-        <v>12.42500000000001</v>
+        <v>22.84828627572657</v>
       </c>
       <c r="G51" t="n">
-        <v>0.09454061251664447</v>
+        <v>1.22237017310253</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="52">
@@ -2555,35 +2655,37 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.008403360933196829</v>
+        <v>0.1941176427455018</v>
       </c>
       <c r="D52" t="n">
-        <v>2.960553565183628e-265</v>
+        <v>0.009029607958494362</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3465096652507782</v>
+        <v>0.5965020060539246</v>
       </c>
       <c r="F52" t="n">
-        <v>12.42500000000001</v>
+        <v>31.85625000000002</v>
       </c>
       <c r="G52" t="n">
-        <v>0.05148658448150834</v>
+        <v>0.4263959390862944</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2134831460674157</v>
       </c>
     </row>
     <row r="53">
@@ -2596,27 +2698,29 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.1588235269448097</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>2.876839432916431e-05</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3215235471725464</v>
+        <v>0.5168488025665283</v>
       </c>
       <c r="F53" t="n">
-        <v>12.42500000000001</v>
+        <v>25.57649647887325</v>
       </c>
       <c r="G53" t="n">
-        <v>0.03788687299893276</v>
+        <v>0.1616862326574173</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
@@ -2624,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.0728476821192053</v>
       </c>
     </row>
     <row r="54">
@@ -2637,35 +2741,37 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.2090395431759713</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>2.084042041730364e-79</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3136659562587738</v>
+        <v>0.6238571405410767</v>
       </c>
       <c r="F54" t="n">
-        <v>12.42500000000001</v>
+        <v>0.5445535714285938</v>
       </c>
       <c r="G54" t="n">
-        <v>0.05224429727740986</v>
+        <v>0.6600441501103753</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2622950819672131</v>
       </c>
     </row>
     <row r="55">
@@ -2678,35 +2784,37 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.2412868586089169</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>6.245369322936759e-156</v>
       </c>
       <c r="E55" t="n">
-        <v>0.3323594033718109</v>
+        <v>0.6119844317436218</v>
       </c>
       <c r="F55" t="n">
-        <v>12.42500000000001</v>
+        <v>33.69093548387099</v>
       </c>
       <c r="G55" t="n">
-        <v>0.04592496765847348</v>
+        <v>0.4695989650711513</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2156862745098039</v>
       </c>
     </row>
     <row r="56">
@@ -2719,35 +2827,37 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.1971014452331864</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>2.626892551353189e-80</v>
       </c>
       <c r="E56" t="n">
-        <v>0.315963089466095</v>
+        <v>0.5822121500968933</v>
       </c>
       <c r="F56" t="n">
-        <v>12.42500000000001</v>
+        <v>17.59505376344089</v>
       </c>
       <c r="G56" t="n">
-        <v>0.04530950861518826</v>
+        <v>0.364390555201021</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2941176470588235</v>
       </c>
     </row>
     <row r="57">
@@ -2760,35 +2870,37 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>0.181818178462272</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1.153567111099626e-80</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3651198446750641</v>
+        <v>0.5616248250007629</v>
       </c>
       <c r="F57" t="n">
-        <v>12.42500000000001</v>
+        <v>23.91363636363641</v>
       </c>
       <c r="G57" t="n">
-        <v>0.02446588559614059</v>
+        <v>0.2467263955892488</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.2432432432432433</v>
       </c>
     </row>
     <row r="58">
@@ -2801,35 +2913,37 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.0120481921868196</v>
+        <v>0.1634241198334571</v>
       </c>
       <c r="D58" t="n">
-        <v>3.542014107114671e-257</v>
+        <v>9.10883278677377e-156</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3421286642551422</v>
+        <v>0.5662688612937927</v>
       </c>
       <c r="F58" t="n">
-        <v>12.42500000000001</v>
+        <v>15.26577922077925</v>
       </c>
       <c r="G58" t="n">
-        <v>0.07667386609071274</v>
+        <v>0.6015118790496761</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="59">
@@ -2842,35 +2956,37 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>0.0978260827221174</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1.502178278808791e-232</v>
       </c>
       <c r="E59" t="n">
-        <v>0.365123987197876</v>
+        <v>0.5114860534667969</v>
       </c>
       <c r="F59" t="n">
-        <v>12.42500000000001</v>
+        <v>23.51032608695655</v>
       </c>
       <c r="G59" t="n">
-        <v>0.08964646464646464</v>
+        <v>0.4419191919191919</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="60">
@@ -2883,27 +2999,29 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.00446428549356267</v>
+        <v>0.1699819136304034</v>
       </c>
       <c r="D60" t="n">
-        <v>8.265132997605698e-314</v>
+        <v>1.059108558790827e-80</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3449465930461884</v>
+        <v>0.5727046132087708</v>
       </c>
       <c r="F60" t="n">
-        <v>12.42500000000001</v>
+        <v>31.1515</v>
       </c>
       <c r="G60" t="n">
-        <v>0.02480782669461915</v>
+        <v>0.2124388539482879</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
@@ -2911,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="61">
@@ -2924,35 +3042,37 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>0.1694915217164609</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>2.641122902589137e-155</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3740620315074921</v>
+        <v>0.4670159816741943</v>
       </c>
       <c r="F61" t="n">
-        <v>12.42500000000001</v>
+        <v>42.60887931034486</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2874493927125506</v>
+        <v>1.983805668016194</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>0.975</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.1240875912408759</v>
       </c>
     </row>
     <row r="62">
@@ -2965,35 +3085,37 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>0.159663861293341</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>2.360787777620462e-155</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3254433572292328</v>
+        <v>0.5814318060874939</v>
       </c>
       <c r="F62" t="n">
-        <v>12.42500000000001</v>
+        <v>34.4511641791045</v>
       </c>
       <c r="G62" t="n">
-        <v>0.1775</v>
+        <v>2.44</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2307692307692308</v>
       </c>
     </row>
     <row r="63">
@@ -3006,27 +3128,29 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>0.2472727222780827</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>4.252812121486095e-155</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3147302865982056</v>
+        <v>0.5911986231803894</v>
       </c>
       <c r="F63" t="n">
-        <v>12.42500000000001</v>
+        <v>42.45704736547088</v>
       </c>
       <c r="G63" t="n">
-        <v>0.09902370990237098</v>
+        <v>1.118549511854951</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
@@ -3034,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2380952380952381</v>
       </c>
     </row>
     <row r="64">
@@ -3047,35 +3171,37 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>0.2327586157030322</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>0.02405625328689112</v>
       </c>
       <c r="E64" t="n">
-        <v>0.310442179441452</v>
+        <v>0.5778536796569824</v>
       </c>
       <c r="F64" t="n">
-        <v>12.42500000000001</v>
+        <v>21.71871273712742</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1163934426229508</v>
+        <v>1.132786885245902</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.186046511627907</v>
       </c>
     </row>
     <row r="65">
@@ -3088,35 +3214,37 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>0.1810344779384662</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>8.109369275808355e-79</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3207126259803772</v>
+        <v>0.567719042301178</v>
       </c>
       <c r="F65" t="n">
-        <v>12.42500000000001</v>
+        <v>28.33250000000004</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1422845691382766</v>
+        <v>1.543086172344689</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1509433962264151</v>
       </c>
     </row>
     <row r="66">
@@ -3129,35 +3257,37 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>0.2509803872861208</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>6.261661583609849e-79</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3186623752117157</v>
+        <v>0.5955936908721924</v>
       </c>
       <c r="F66" t="n">
-        <v>12.42500000000001</v>
+        <v>33.91318987341774</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0890840652446675</v>
+        <v>0.7540777917189461</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.148936170212766</v>
       </c>
     </row>
     <row r="67">
@@ -3170,35 +3300,37 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>0.2328767074047665</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>4.015646547179402e-155</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3204876482486725</v>
+        <v>0.6221136450767517</v>
       </c>
       <c r="F67" t="n">
-        <v>12.42500000000001</v>
+        <v>43.80500000000004</v>
       </c>
       <c r="G67" t="n">
-        <v>0.09726027397260274</v>
+        <v>1.306849315068493</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3396226415094339</v>
       </c>
     </row>
     <row r="68">
@@ -3211,35 +3343,37 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>0.09259259020061734</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>8.06798322521923e-232</v>
       </c>
       <c r="E68" t="n">
-        <v>0.3620995283126831</v>
+        <v>0.4935102164745331</v>
       </c>
       <c r="F68" t="n">
-        <v>12.42500000000001</v>
+        <v>9.262820329277048</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5590551181102362</v>
+        <v>4.503937007874016</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3103448275862069</v>
       </c>
     </row>
   </sheetData>
